--- a/data/numeric/input/old_data_99/【抖音教育项目】数据源_desensitized.xlsx
+++ b/data/numeric/input/old_data_99/【抖音教育项目】数据源_desensitized.xlsx
@@ -2692,13 +2692,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71565325-ECC7-4A20-9F36-427E87C29530}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7A59E0C-1C23-46E8-A161-F43956A448FF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87B6A3D-B5D1-4979-A5C3-E8E608E8D2F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9859D543-01A0-4FCA-9E9F-A26F2797956D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37C3E387-6849-44B0-9AD9-0B8BF1ED44DF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4F5D4D22-4638-45E8-AEA1-BF30895159DD}"/>
 </file>